--- a/publication/web-root/matchsync-donor/0.1.0/CodeSystem-nmdp-order-type.xlsx
+++ b/publication/web-root/matchsync-donor/0.1.0/CodeSystem-nmdp-order-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://terminology.nmdp.org/codesystem/order-type</t>
+    <t>http://fhir.nmdp.org/CodeSystem/order-type</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T19:29:11+00:00</t>
+    <t>2026-09-03T14:51:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Codes identifying the type of donor workup or collection order in the NMDP system.</t>
+    <t>Codes identifying the type of donor or CBU workup order in the NMDP system.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -120,7 +120,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>5</t>
+    <t>9</t>
   </si>
   <si>
     <t>Level</t>
@@ -138,7 +138,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>ct</t>
+    <t>confirmatory-typing</t>
   </si>
   <si>
     <t>Confirmatory Typing</t>
@@ -181,6 +181,42 @@
   </si>
   <si>
     <t>Bone marrow harvest collection.</t>
+  </si>
+  <si>
+    <t>A-HR</t>
+  </si>
+  <si>
+    <t>HLA-A High Resolution</t>
+  </si>
+  <si>
+    <t>HLA-A high resolution typing order for CBU.</t>
+  </si>
+  <si>
+    <t>B-HR</t>
+  </si>
+  <si>
+    <t>HLA-B High Resolution</t>
+  </si>
+  <si>
+    <t>HLA-B high resolution typing order for CBU.</t>
+  </si>
+  <si>
+    <t>C-HR</t>
+  </si>
+  <si>
+    <t>HLA-C High Resolution</t>
+  </si>
+  <si>
+    <t>HLA-C high resolution typing order for CBU.</t>
+  </si>
+  <si>
+    <t>ABC-DRB1-DQB1-DPB1-HR</t>
+  </si>
+  <si>
+    <t>Full Panel High Resolution</t>
+  </si>
+  <si>
+    <t>Full panel high resolution typing (HLA-A, B, C, DRB1, DQB1, DPB1) order for CBU.</t>
   </si>
 </sst>
 </file>
@@ -488,7 +524,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -575,6 +611,62 @@
         <v>55</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/publication/web-root/matchsync-donor/0.1.0/CodeSystem-nmdp-order-type.xlsx
+++ b/publication/web-root/matchsync-donor/0.1.0/CodeSystem-nmdp-order-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:51:12+00:00</t>
+    <t>2026-09-03T16:43:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
